--- a/output/pdf_financials_xlsx/KRI.xlsx
+++ b/output/pdf_financials_xlsx/KRI.xlsx
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.451529</v>
+        <v>-1.451529</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-4.807305</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.451529</v>
+        <v>-1.451529</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-4.807305</v>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.451529</v>
+        <v>-1.451529</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-4.807305</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.451529</v>
+        <v>-1.451529</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-4.807305</v>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.451529</v>
+        <v>-1.451529</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-4.807305</v>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="H180" s="5" t="n">
-        <v>1.451529</v>
+        <v>-1.451529</v>
       </c>
       <c r="I180" s="5" t="n">
         <v>-4.80729</v>
@@ -14512,10 +14512,10 @@
         </is>
       </c>
       <c r="H196" s="5" t="n">
-        <v>1.451529</v>
+        <v>-1.451529</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>4.807305</v>
+        <v>-4.807305</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/KRI.xlsx
+++ b/output/pdf_financials_xlsx/KRI.xlsx
@@ -1552,25 +1552,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.730664</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002097</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.506915</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.260284</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.130659</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.099232</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.326474</v>
       </c>
     </row>
     <row r="35">
@@ -1608,25 +1608,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.730664</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002097</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.506915</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.260284</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.130659</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.099232</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.326474</v>
       </c>
     </row>
     <row r="37">
@@ -1950,19 +1950,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.632966</v>
+        <v>0.126051</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.283299</v>
+        <v>0.023015</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.05679</v>
+        <v>0.926131</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.641166</v>
+        <v>2.541934</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.823092</v>
+        <v>0.496618</v>
       </c>
     </row>
     <row r="49">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">

--- a/output/pdf_financials_xlsx/KRI.xlsx
+++ b/output/pdf_financials_xlsx/KRI.xlsx
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.023888</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.032846</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.069121</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.142375</v>
       </c>
     </row>
     <row r="29">
@@ -1408,16 +1408,16 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.451529</v>
+        <v>-1.427641</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.807305</v>
+        <v>-4.774459</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.596149</v>
+        <v>-5.527028</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.993218</v>
+        <v>-7.850843</v>
       </c>
     </row>
     <row r="30">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.023888</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.032846</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.069121</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.142375</v>
       </c>
     </row>
     <row r="101">
@@ -9180,7 +9180,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -12565,7 +12569,11 @@
           <t>Depreciation of property, plant and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -13161,7 +13169,11 @@
           <t>Depreciation of property, plant and equipment (note 5) $</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -13822,7 +13834,11 @@
           <t>Depreciation of property, plant and equipment (note 4) $</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KRI.xlsx
+++ b/output/pdf_financials_xlsx/KRI.xlsx
@@ -504,20 +504,16 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -538,20 +534,16 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -572,20 +564,16 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -606,20 +594,16 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.000174</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0.249144</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.269185</v>
@@ -640,20 +624,16 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -674,20 +654,16 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -708,20 +684,16 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.000174</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>0.249144</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>1.455146</v>
@@ -742,20 +714,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.000174</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-0.249144</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-1.455146</v>
@@ -776,20 +744,16 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -810,20 +774,16 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>-0</v>
@@ -844,20 +804,16 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -878,20 +834,16 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>-0.000958</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>-0.000307</v>
@@ -912,20 +864,16 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.154451</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" s="3" t="n">
+        <v>-1.466582</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.451529</v>
@@ -946,20 +894,16 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1064,20 +1008,16 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.154451</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>-1.466582</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.451529</v>
@@ -1098,20 +1038,16 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1132,20 +1068,16 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -1174,10 +1106,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" s="3" t="n">
+        <v>-1.466582</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.451529</v>
@@ -1198,10 +1128,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
@@ -1240,10 +1168,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
@@ -1282,10 +1208,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>3.861275</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1324,20 +1248,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.154451</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D27" s="3" t="n">
+        <v>-1.466582</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.451529</v>
@@ -1358,20 +1278,16 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0.023371</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.023888</v>
@@ -1392,20 +1308,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.154451</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D29" s="3" t="n">
+        <v>-1.443211</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.427641</v>
@@ -1468,20 +1380,16 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -3418,10 +3326,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-1.466582</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-1.451529</v>
@@ -3448,10 +3354,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0.023371</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0.023888</v>
@@ -3478,10 +3382,8 @@
       <c r="C101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>0</v>
@@ -3508,10 +3410,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0</v>
@@ -3538,10 +3438,8 @@
       <c r="C103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -3568,13 +3466,11 @@
       <c r="C104" s="3" t="n">
         <v>-0.049258</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0.375027</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0</v>
+        <v>0.35933</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>0</v>
@@ -3598,10 +3494,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E105" s="3" t="n">
         <v>0</v>
@@ -3628,13 +3522,11 @@
       <c r="C106" s="3" t="n">
         <v>-0.108567</v>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>0.35795</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>0.374787</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>0</v>
@@ -3658,10 +3550,8 @@
       <c r="C107" s="3" t="n">
         <v>0.033279</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0.221576</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.163673</v>
@@ -3688,10 +3578,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -3718,10 +3606,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>0</v>
@@ -3748,10 +3634,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -3778,10 +3662,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>-0.05649</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3808,10 +3690,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -3838,10 +3718,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -3868,10 +3746,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -3898,10 +3774,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -3928,10 +3802,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -3958,10 +3830,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E117" s="3" t="n">
         <v>0</v>
@@ -3988,10 +3858,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0</v>
@@ -4050,10 +3918,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -4080,10 +3946,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -4110,10 +3974,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -4140,10 +4002,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -4170,10 +4030,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -4200,10 +4058,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -4230,10 +4086,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>
@@ -4302,10 +4156,8 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>-0.006719</v>
@@ -4398,10 +4250,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0</v>
@@ -4428,10 +4278,8 @@
       <c r="C132" s="3" t="n">
         <v>-0.728567</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>0.277277</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>-0.246631</v>
@@ -4490,10 +4338,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>-0.05649</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -4524,10 +4370,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.920175</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.676173</v>
@@ -4553,7 +4397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K226"/>
+  <dimension ref="A1:K261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9146,10 +8990,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G90" s="5" t="n">
+        <v>0.221576</v>
       </c>
       <c r="H90" s="5" t="n">
         <v>0.163673</v>
@@ -9195,10 +9037,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G91" s="5" t="n">
+        <v>0.023371</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>0.023888</v>
@@ -9726,10 +9566,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="5" t="n">
+        <v>-0.05649</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -10693,10 +10531,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="5" t="n">
+        <v>1.255245</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>0.52275</v>
@@ -11052,10 +10888,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="5" t="n">
+        <v>0.004899</v>
       </c>
       <c r="H128" s="5" t="n">
         <v>0.006119</v>
@@ -11413,10 +11247,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="5" t="n">
+        <v>-0.07636</v>
       </c>
       <c r="H135" s="5" t="n">
         <v>-0.128989</v>
@@ -11443,28 +11275,36 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>For the year ended December 31, 2019 and for the period from April 27, 2018 to December</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>-1.466582</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>-1.451529</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -11490,36 +11330,30 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Amortization of deferred government grant</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Amortization of deferred government grant income</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F137" s="5" t="n">
-        <v>0.033279</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-0.004899</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>-0.006119</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -11545,34 +11379,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Amortization of deferred government grant</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>0.069008</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>-0.049258</v>
+          <t>Gain on sale of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H138" s="5" t="n">
+        <v>-0.002341</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -11598,34 +11430,30 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Amortization of deferred government grant</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items total</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="n">
-        <v>-0.08544300000000001</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>-0.108567</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization of deferred government grant total</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>-1.221635</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>-1.05096</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -11651,12 +11479,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non –cash working capital items</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Investment in short-term GIC</t>
+          <t>Commodity taxes receivable</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -11665,18 +11493,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F140" s="5" t="n">
-        <v>-0.625</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>-0.019821</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>0.016676</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -11702,12 +11528,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non –cash working capital items</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Proceeds from partial redemption of GIC</t>
+          <t>Advances to a director</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -11716,13 +11542,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F141" s="5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.003122</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -11753,17 +11579,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non –cash working capital items</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Investing activities total</t>
+          <t>Accounts payable</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -11771,18 +11597,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F142" s="5" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.375027</v>
+      </c>
+      <c r="H142" s="5" t="n">
+        <v>0.35933</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -11808,32 +11632,30 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non –cash working capital items</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of common shares and net cash provided by financing activities, net of issue costs</t>
+          <t>Advances from a director and a consultant</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="n">
-        <v>0.816107</v>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G143" s="5" t="n">
+        <v>-0.000378</v>
+      </c>
+      <c r="H143" s="5" t="n">
+        <v>-0.001219</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -11859,34 +11681,34 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non –cash working capital items</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net changes in cash</t>
+          <t>Changes in non –cash working capital items total</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>0.730664</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>-0.728567</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="H144" s="5" t="n">
+        <v>0.374787</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -11912,32 +11734,34 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non –cash working capital items</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cash, beginning of year/period</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F145" s="5" t="n">
-        <v>0.730664</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-0.863685</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>-0.676173</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -11963,25 +11787,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cash, end of year/period</t>
+          <t>Security deposits</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="n">
-        <v>0.730664</v>
-      </c>
-      <c r="F146" s="5" t="n">
-        <v>0.002097</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>-0.001433</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -12012,30 +11838,32 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2.    Basis of presentation</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2.    Basis of presentation total</t>
+          <t>Proceed from sale of property, plant and equipment</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>0.00202</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>2.9e-05</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H147" s="5" t="n">
+        <v>0.0425</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -12061,36 +11889,30 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>-0.154451</v>
+          <t>Net cash generated from (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G148" s="5" t="n">
+        <v>-0.057923</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>0.0425</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -12121,26 +11943,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net changes in cash, cash end of period</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>0.730664</v>
+          <t>Long-term debt</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G149" s="5" t="n">
+        <v>0.02</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -12171,32 +11989,30 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1.    Nature of operations</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>a Qualifying Transaction. The Exchange may suspend or delist the Company’s shares from trading should it not meet these requirements. Moreover, The Company has incurred a net loss of $154,451 during the 8-month period ended December</t>
+          <t>Net cash generated from financing activities</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G150" s="5" t="n">
+        <v>1.198885</v>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>0.387042</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -12222,32 +12038,34 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>which is the functional currency of the Company.</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Directors on April 19,</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>0.002019</v>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G151" s="5" t="n">
+        <v>0.277277</v>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>-0.246631</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -12268,17 +12086,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Exploration expenses (note 13) $</t>
+          <t>Cash at the beginning of year</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -12292,49 +12110,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G152" s="5" t="n">
+        <v>0.229638</v>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>0.506915</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J152" s="5" t="n">
-        <v>4.276975</v>
-      </c>
-      <c r="K152" s="5" t="n">
-        <v>5.898455</v>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Professional fees (note 13)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Cash at the end of year</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12345,45 +12159,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G153" s="5" t="n">
+        <v>0.506915</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>0.373182</v>
-      </c>
-      <c r="I153" s="5" t="n">
-        <v>0.406379</v>
-      </c>
-      <c r="J153" s="5" t="n">
-        <v>0.300142</v>
-      </c>
-      <c r="K153" s="5" t="n">
-        <v>0.5802079999999999</v>
+        <v>0.260284</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Transactions not affecting cash</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Subscription receivable</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -12394,47 +12208,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G154" s="5" t="n">
+        <v>-0.02</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I154" s="5" t="n">
-        <v>0.24566</v>
-      </c>
-      <c r="J154" s="5" t="n">
-        <v>0.303701</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>0.423029</v>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Transactions not affecting cash</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 13)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accounts payable to directors converted in shares (note 9)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -12445,144 +12259,156 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H155" s="5" t="n">
-        <v>0.266376</v>
-      </c>
-      <c r="I155" s="5" t="n">
-        <v>0.420557</v>
-      </c>
-      <c r="J155" s="5" t="n">
-        <v>0.325111</v>
-      </c>
-      <c r="K155" s="5" t="n">
-        <v>0.359468</v>
+      <c r="G155" s="5" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Share-based compensation (notes 9 and 13)</t>
+          <t>For the year ended December 31, 2019 and for the period from April 27, 2018 to December</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E156" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H156" s="5" t="n">
-        <v>0.163673</v>
-      </c>
-      <c r="I156" s="5" t="n">
-        <v>0.522048</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>0.183099</v>
-      </c>
-      <c r="K156" s="5" t="n">
-        <v>0.356156</v>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Office and travelling expenses</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F157" s="5" t="n">
+        <v>0.033279</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H157" s="5" t="n">
-        <v>0.114246</v>
-      </c>
-      <c r="I157" s="5" t="n">
-        <v>0.13963</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>0.203435</v>
-      </c>
-      <c r="K157" s="5" t="n">
-        <v>0.268946</v>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment (note 5)</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="n">
+        <v>0.069008</v>
+      </c>
+      <c r="F158" s="5" t="n">
+        <v>-0.049258</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -12599,137 +12425,145 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J158" s="5" t="n">
-        <v>0.069121</v>
-      </c>
-      <c r="K158" s="5" t="n">
-        <v>0.142375</v>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sundry taxes</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net change in non-cash working capital items total</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="n">
+        <v>-0.08544300000000001</v>
+      </c>
+      <c r="F159" s="5" t="n">
+        <v>-0.108567</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H159" s="5" t="n">
-        <v>0.017696</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>0.023468</v>
-      </c>
-      <c r="J159" s="5" t="n">
-        <v>0.010168</v>
-      </c>
-      <c r="K159" s="5" t="n">
-        <v>0.024924</v>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Investment in short-term GIC</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F160" s="5" t="n">
+        <v>-0.625</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H160" s="5" t="n">
-        <v>1.455146</v>
-      </c>
-      <c r="I160" s="5" t="n">
-        <v>4.534277</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>5.671752</v>
-      </c>
-      <c r="K160" s="5" t="n">
-        <v>8.053561</v>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Other (expenses) income</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bank charges</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Proceeds from partial redemption of GIC</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F161" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -12741,35 +12575,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="5" t="n">
-        <v>0.010259</v>
-      </c>
-      <c r="J161" s="5" t="n">
-        <v>0.015644</v>
-      </c>
-      <c r="K161" s="5" t="n">
-        <v>0.01935</v>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Other (expenses) income</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Investing activities total</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -12777,10 +12617,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F162" s="5" t="n">
+        <v>-0.62</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -12792,41 +12630,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="5" t="n">
-        <v>-0.00167</v>
-      </c>
-      <c r="J162" s="5" t="n">
-        <v>-0.011994</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>-0.004681</v>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Other (expenses) income</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from issuance of common shares and net cash provided by financing activities, net of issue costs</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" s="5" t="n">
+        <v>0.816107</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12843,46 +12681,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="5" t="n">
-        <v>0.07141599999999999</v>
-      </c>
-      <c r="J163" s="5" t="n">
-        <v>0.103241</v>
-      </c>
-      <c r="K163" s="5" t="n">
-        <v>0.084374</v>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Other (expenses) income</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Net changes in cash</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>0.730664</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>-0.728567</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -12899,27 +12739,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J164" s="5" t="n">
-        <v>-5.596149</v>
-      </c>
-      <c r="K164" s="5" t="n">
-        <v>-7.993218</v>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Exchange difference on translating foreign operations $</t>
+          <t>Cash, beginning of year/period</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12928,10 +12772,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F165" s="5" t="n">
+        <v>0.730664</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -12943,46 +12785,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="5" t="n">
-        <v>1.5e-05</v>
-      </c>
-      <c r="J165" s="5" t="n">
-        <v>-0.456983</v>
-      </c>
-      <c r="K165" s="5" t="n">
-        <v>0.5460930000000001</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, end of year/period</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" s="5" t="n">
+        <v>0.730664</v>
+      </c>
+      <c r="F166" s="5" t="n">
+        <v>0.002097</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -12999,43 +12839,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J166" s="5" t="n">
-        <v>-0.456983</v>
-      </c>
-      <c r="K166" s="5" t="n">
-        <v>0.5460930000000001</v>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>2.    Basis of presentation</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2.    Basis of presentation total</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>2.9e-05</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -13052,34 +12888,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J167" s="5" t="n">
-        <v>-6.053132</v>
-      </c>
-      <c r="K167" s="5" t="n">
-        <v>-7.447125</v>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 12) $</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n">
+        <v>-0.154451</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13091,44 +12933,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H168" s="5" t="n">
-        <v>3e-08</v>
-      </c>
-      <c r="I168" s="5" t="n">
-        <v>5.999999999999999e-08</v>
-      </c>
-      <c r="J168" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="K168" s="5" t="n">
-        <v>-7e-08</v>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (note 12)</t>
+          <t>Net changes in cash, cash end of period</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n">
+        <v>0.730664</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13140,44 +12988,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" s="5" t="n">
-        <v>54.210321</v>
-      </c>
-      <c r="I169" s="5" t="n">
-        <v>75.075453</v>
-      </c>
-      <c r="J169" s="5" t="n">
-        <v>98.202607</v>
-      </c>
-      <c r="K169" s="5" t="n">
-        <v>112.052234</v>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>1.    Nature of operations</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment (note 5) $</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>a Qualifying Transaction. The Exchange may suspend or delist the Company’s shares from trading should it not meet these requirements. Moreover, The Company has incurred a net loss of $154,451 during the 8-month period ended December</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13194,11 +13044,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I170" s="5" t="n">
-        <v>0.032846</v>
-      </c>
-      <c r="J170" s="5" t="n">
-        <v>0.069121</v>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -13209,24 +13063,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>which is the functional currency of the Company.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Exploration expenses (note 14)</t>
+          <t>Directors on April 19,</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E171" s="5" t="n">
+        <v>0.002019</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13243,11 +13095,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="5" t="n">
-        <v>2.444277</v>
-      </c>
-      <c r="J171" s="5" t="n">
-        <v>4.276975</v>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -13268,14 +13124,10 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Management and consulting fees (note 14)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration expenses (note 13) $</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -13296,16 +13148,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I172" s="5" t="n">
-        <v>0.420557</v>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J172" s="5" t="n">
-        <v>0.325111</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.276975</v>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>5.898455</v>
       </c>
     </row>
     <row r="173">
@@ -13321,7 +13173,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Professional fees (note 14)</t>
+          <t>Professional fees (note 13)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -13344,10 +13196,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H173" s="5" t="n">
+        <v>0.373182</v>
       </c>
       <c r="I173" s="5" t="n">
         <v>0.406379</v>
@@ -13355,10 +13205,8 @@
       <c r="J173" s="5" t="n">
         <v>0.300142</v>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K173" s="5" t="n">
+        <v>0.5802079999999999</v>
       </c>
     </row>
     <row r="174">
@@ -13374,10 +13222,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Share-based compensation (notes 10 and 14)</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -13399,15 +13251,13 @@
         </is>
       </c>
       <c r="I174" s="5" t="n">
-        <v>0.522048</v>
+        <v>0.24566</v>
       </c>
       <c r="J174" s="5" t="n">
-        <v>0.183099</v>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.303701</v>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>0.423029</v>
       </c>
     </row>
     <row r="175">
@@ -13423,10 +13273,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Transaction costs (note 1)</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>Management and consulting fees (note 13)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -13442,23 +13296,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H175" s="5" t="n">
+        <v>0.266376</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>0.299412</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.420557</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>0.325111</v>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>0.359468</v>
       </c>
     </row>
     <row r="176">
@@ -13469,12 +13317,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Other (expenses) income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Listing costs expensed (note 1)</t>
+          <t>Share-based compensation (notes 9 and 13)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13493,23 +13341,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H176" s="5" t="n">
+        <v>0.163673</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>-0.352515</v>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.522048</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>0.183099</v>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>0.356156</v>
       </c>
     </row>
     <row r="177">
@@ -13520,12 +13362,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Other (expenses) income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Write-off of CEBA grant (note 7)</t>
+          <t>Office and travelling expenses</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -13544,23 +13386,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H177" s="5" t="n">
+        <v>0.114246</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.13963</v>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>0.203435</v>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>0.268946</v>
       </c>
     </row>
     <row r="178">
@@ -13571,17 +13407,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Other (expenses) income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
+          <t>Depreciation of property, plant and equipment (note 5)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -13604,16 +13440,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I178" s="5" t="n">
-        <v>-4.807305</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J178" s="5" t="n">
-        <v>-5.596149</v>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.069121</v>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>0.142375</v>
       </c>
     </row>
     <row r="179">
@@ -13624,12 +13460,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) income for the period</t>
+          <t>Sundry taxes</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -13648,21 +13484,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H179" s="5" t="n">
+        <v>0.017696</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>1.5e-05</v>
+        <v>0.023468</v>
       </c>
       <c r="J179" s="5" t="n">
-        <v>-0.456983</v>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010168</v>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>0.024924</v>
       </c>
     </row>
     <row r="180">
@@ -13673,17 +13505,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the period $</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -13702,18 +13534,16 @@
         </is>
       </c>
       <c r="H180" s="5" t="n">
-        <v>-1.451529</v>
+        <v>1.455146</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>-4.80729</v>
+        <v>4.534277</v>
       </c>
       <c r="J180" s="5" t="n">
-        <v>-6.053132</v>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.671752</v>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>8.053561</v>
       </c>
     </row>
     <row r="181">
@@ -13724,15 +13554,19 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Other (expenses) income</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share (note 13) $</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -13754,15 +13588,13 @@
         </is>
       </c>
       <c r="I181" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.010259</v>
       </c>
       <c r="J181" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.015644</v>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>0.01935</v>
       </c>
     </row>
     <row r="182">
@@ -13773,17 +13605,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Other (expenses) income</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding (note 13)</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -13807,15 +13639,13 @@
         </is>
       </c>
       <c r="I182" s="5" t="n">
-        <v>75.075453</v>
+        <v>-0.00167</v>
       </c>
       <c r="J182" s="5" t="n">
-        <v>98.202607</v>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.011994</v>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>-0.004681</v>
       </c>
     </row>
     <row r="183">
@@ -13826,17 +13656,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other (expenses) income</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment (note 4) $</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>DepreciationAmortizationDepletion</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -13854,21 +13684,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H183" s="5" t="n">
-        <v>0.023888</v>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I183" s="5" t="n">
-        <v>0.032846</v>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07141599999999999</v>
+      </c>
+      <c r="J183" s="5" t="n">
+        <v>0.103241</v>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>0.084374</v>
       </c>
     </row>
     <row r="184">
@@ -13879,15 +13707,19 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other (expenses) income</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Exploration expenses (note 13)</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -13903,21 +13735,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H184" s="5" t="n">
-        <v>0.276958</v>
-      </c>
-      <c r="I184" s="5" t="n">
-        <v>2.444277</v>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="n">
+        <v>-5.596149</v>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>-7.993218</v>
       </c>
     </row>
     <row r="185">
@@ -13928,12 +13760,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
+          <t>Exchange difference on translating foreign operations $</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13958,17 +13790,13 @@
         </is>
       </c>
       <c r="I185" s="5" t="n">
-        <v>0.299412</v>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.5e-05</v>
+      </c>
+      <c r="J185" s="5" t="n">
+        <v>-0.456983</v>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>0.5460930000000001</v>
       </c>
     </row>
     <row r="186">
@@ -13979,15 +13807,19 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Write-off of deferred expenses (note 8)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Other comprehensive income (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -14003,23 +13835,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H186" s="5" t="n">
-        <v>0.215349</v>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J186" s="5" t="n">
+        <v>-0.456983</v>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>0.5460930000000001</v>
       </c>
     </row>
     <row r="187">
@@ -14030,15 +13860,19 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Interest on long-term debt</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Total comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -14054,23 +13888,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H187" s="5" t="n">
-        <v>0.006119</v>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J187" s="5" t="n">
+        <v>-6.053132</v>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>-7.447125</v>
       </c>
     </row>
     <row r="188">
@@ -14081,12 +13913,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Gain on sale of property, plant and equipment</t>
+          <t>Basic and diluted net loss per share (note 12) $</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -14106,22 +13938,16 @@
         </is>
       </c>
       <c r="H188" s="5" t="n">
-        <v>-0.002341</v>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-08</v>
+      </c>
+      <c r="I188" s="5" t="n">
+        <v>5.999999999999999e-08</v>
+      </c>
+      <c r="J188" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>-7e-08</v>
       </c>
     </row>
     <row r="189">
@@ -14132,15 +13958,19 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Listing costs expensed (note 1)</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding (note 12)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -14156,23 +13986,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H189" s="5" t="n">
+        <v>54.210321</v>
       </c>
       <c r="I189" s="5" t="n">
-        <v>0.352515</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>75.075453</v>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>98.202607</v>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>112.052234</v>
       </c>
     </row>
     <row r="190">
@@ -14183,17 +14007,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Depreciation of property, plant and equipment (note 5) $</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -14211,16 +14035,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="5" t="n">
-        <v>0.002809</v>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I190" s="5" t="n">
-        <v>0.010259</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.032846</v>
+      </c>
+      <c r="J190" s="5" t="n">
+        <v>0.069121</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14236,19 +14060,15 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Exploration expenses (note 14)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -14264,16 +14084,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H191" s="5" t="n">
-        <v>-0.000307</v>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I191" s="5" t="n">
-        <v>0.00167</v>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.444277</v>
+      </c>
+      <c r="J191" s="5" t="n">
+        <v>4.276975</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14289,15 +14109,19 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Write-off of CEBA grant (note 6)</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
+          <t>Management and consulting fees (note 14)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -14319,12 +14143,10 @@
         </is>
       </c>
       <c r="I192" s="5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.420557</v>
+      </c>
+      <c r="J192" s="5" t="n">
+        <v>0.325111</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14340,17 +14162,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Professional fees (note 14)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -14374,12 +14196,10 @@
         </is>
       </c>
       <c r="I193" s="5" t="n">
-        <v>-0.07141599999999999</v>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.406379</v>
+      </c>
+      <c r="J193" s="5" t="n">
+        <v>0.300142</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14395,12 +14215,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Amortization of deferred government grant income</t>
+          <t>Share-based compensation (notes 10 and 14)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -14419,18 +14239,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" s="5" t="n">
-        <v>-0.006119</v>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="n">
+        <v>0.522048</v>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>0.183099</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14446,19 +14264,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Other income/expenses total</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Transaction costs (note 1)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -14474,11 +14288,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="5" t="n">
-        <v>1.451529</v>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I195" s="5" t="n">
-        <v>4.807305</v>
+        <v>0.299412</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -14499,19 +14315,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Other income/expenses</t>
+          <t>Other (expenses) income</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Listing costs expensed (note 1)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -14527,11 +14339,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H196" s="5" t="n">
-        <v>-1.451529</v>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I196" s="5" t="n">
-        <v>-4.807305</v>
+        <v>-0.352515</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -14552,12 +14366,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Items that will be reclassified subsequently to loss</t>
+          <t>Other (expenses) income</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Other comprehensive income for the period</t>
+          <t>Write-off of CEBA grant (note 7)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -14582,7 +14396,7 @@
         </is>
       </c>
       <c r="I197" s="5" t="n">
-        <v>-1.5e-05</v>
+        <v>0.02</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -14603,15 +14417,19 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>shares        capital       options      warrants        loss            deficit        Total</t>
+          <t>Other (expenses) income</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 54,195,999 $ 5,748,715 $ 483,638 $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -14627,16 +14445,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H198" s="5" t="n">
-        <v>0.040166</v>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I198" s="5" t="n">
-        <v>-6.192187</v>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.807305</v>
+      </c>
+      <c r="J198" s="5" t="n">
+        <v>-5.596149</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14652,12 +14470,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>shares        capital       options      warrants        loss            deficit        Total</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Shares issued (note 8) 2,613,750 522,750 - - -</t>
+          <t>Other comprehensive (loss) income for the period</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -14676,18 +14494,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H199" s="5" t="n">
-        <v>0.52275</v>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>1.5e-05</v>
+      </c>
+      <c r="J199" s="5" t="n">
+        <v>-0.456983</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14703,15 +14519,19 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>shares        capital       options      warrants        loss            deficit        Total</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Shares issue costs (note 8) - - - - -</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Total comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -14728,15 +14548,13 @@
         </is>
       </c>
       <c r="H200" s="5" t="n">
-        <v>-0.006719</v>
+        <v>-1.451529</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>-0.006719</v>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.80729</v>
+      </c>
+      <c r="J200" s="5" t="n">
+        <v>-6.053132</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -14752,12 +14570,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>shares        capital       options      warrants        loss            deficit        Total</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 9) - - 163,673 - -</t>
+          <t>Basic and diluted net loss per share (note 13) $</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -14776,18 +14594,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H201" s="5" t="n">
-        <v>0.163673</v>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="J201" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -14803,15 +14619,19 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>shares        capital       options      warrants        loss            deficit        Total</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive for the period - - - - -</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding (note 13)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -14827,16 +14647,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H202" s="5" t="n">
-        <v>-1.451529</v>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I202" s="5" t="n">
-        <v>-1.451529</v>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>75.075453</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>98.202607</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -14852,15 +14672,19 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>shares        capital       options      warrants        loss            deficit        Total</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 56,809,749 6,271,465 647,311 - -</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Depreciation of property, plant and equipment (note 4) $</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -14877,10 +14701,10 @@
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>-0.7316589999999999</v>
+        <v>0.023888</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>-7.650435</v>
+        <v>0.032846</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -14901,12 +14725,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Shares deemed to be issued on reverse</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Shares deemed to be issued on reverse takeover (note 8) 1,413,000 353,250 - - -</t>
+          <t>Exploration expenses (note 13)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -14926,12 +14750,10 @@
         </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>0.35325</v>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.276958</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>2.444277</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -14952,12 +14774,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Shares issued related to concurrent</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Shares issued related to concurrent financing (note 8) 18,705,600 4,676,400 - - -</t>
+          <t>Transaction costs</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -14976,13 +14798,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H205" s="5" t="n">
-        <v>4.6764</v>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>0.299412</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -15003,12 +14825,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Share issue costs related to concurrent</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Share issue costs related to concurrent financing - - - - -</t>
+          <t>Write-off of deferred expenses (note 8)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -15028,10 +14850,12 @@
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>-0.451124</v>
-      </c>
-      <c r="I206" s="5" t="n">
-        <v>-0.451124</v>
+        <v>0.215349</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -15052,12 +14876,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Share issue costs related to concurrent</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Broker warrants granted (note 8) - - - 101,000 -</t>
+          <t>Interest on long-term debt</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -15076,13 +14900,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I207" s="5" t="n">
-        <v>-0.101</v>
+      <c r="H207" s="5" t="n">
+        <v>0.006119</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -15103,12 +14927,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Share issue costs related to concurrent</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Exercise of warrants (note 8) 4,250,034 1,275,010 - - -</t>
+          <t>Gain on sale of property, plant and equipment</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -15128,7 +14952,7 @@
         </is>
       </c>
       <c r="H208" s="5" t="n">
-        <v>1.27501</v>
+        <v>-0.002341</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -15154,12 +14978,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Share issue costs related to concurrent</t>
+          <t>Other income/expenses</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 9) - - 522,048 - -</t>
+          <t>Listing costs expensed (note 1)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -15178,13 +15002,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" s="5" t="n">
-        <v>0.522048</v>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>0.352515</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -15205,17 +15029,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for</t>
+          <t>Other income/expenses</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period - - - - 15</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -15234,10 +15058,10 @@
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>-4.80729</v>
+        <v>0.002809</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>-4.807305</v>
+        <v>0.010259</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -15258,15 +15082,19 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for</t>
+          <t>Other income/expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 81,178,383 $ 12,576,125 $ 1,169,359 $ 101,000 $ 15 $</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -15283,10 +15111,10 @@
         </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>0.836635</v>
+        <v>-0.000307</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>-13.009864</v>
+        <v>0.00167</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -15305,18 +15133,26 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Other income/expenses</t>
+        </is>
+      </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>For the year ended December 31, 2019 and for the period from April 27, 2018 to December</t>
+          <t>Write-off of CEBA grant (note 6)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
-      <c r="E212" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -15328,10 +15164,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I212" s="5" t="n">
+        <v>-0.02</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -15352,20 +15186,28 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income/expenses</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" s="5" t="n">
-        <v>0.068588</v>
-      </c>
-      <c r="F213" s="5" t="n">
-        <v>0.053302</v>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -15377,10 +15219,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I213" s="5" t="n">
+        <v>-0.07141599999999999</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -15401,12 +15241,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income/expenses</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Amortization of deferred government grant income</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -15415,18 +15255,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F214" s="5" t="n">
-        <v>0.033279</v>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H214" s="5" t="n">
+        <v>-0.006119</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -15452,35 +15292,39 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income/expenses</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Listing fees</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" s="5" t="n">
-        <v>0.085689</v>
-      </c>
-      <c r="F215" s="5" t="n">
-        <v>0.005987</v>
+          <t>Other income/expenses total</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>1.451529</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>4.807305</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -15501,35 +15345,39 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income/expenses</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bank charges and interest</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" s="5" t="n">
-        <v>0.000174</v>
-      </c>
-      <c r="F216" s="5" t="n">
-        <v>2e-05</v>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H216" s="5" t="n">
+        <v>-1.451529</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>-4.807305</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -15550,20 +15398,24 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items that will be reclassified subsequently to loss</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Other comprehensive income for the period</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" s="5" t="n">
-        <v>-0.154451</v>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>-0.092588</v>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -15575,10 +15427,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I217" s="5" t="n">
+        <v>-1.5e-05</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -15599,35 +15449,35 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares        capital       options      warrants        loss            deficit        Total</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Basic and fully diluted loss per share (Note 6(c))</t>
+          <t>Balance, December 31, 2021 54,195,999 $ 5,748,715 $ 483,638 $ - $ - $</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="F218" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H218" s="5" t="n">
+        <v>0.040166</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>-6.192187</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -15648,30 +15498,32 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares        capital       options      warrants        loss            deficit        Total</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>For the year ended December 31, 2019 and for the period from April 27, 2018 to December</t>
+          <t>Shares issued (note 8) 2,613,750 522,750 - - -</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
-      <c r="E219" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F219" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H219" s="5" t="n">
+        <v>0.52275</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -15697,12 +15549,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>shares       Capital    Surplus         Warrants      Deficit         equity</t>
+          <t>shares        capital       options      warrants        loss            deficit        Total</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Balance - April 27, 2018 - - - -</t>
+          <t>Shares issue costs (note 8) - - - - -</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -15721,15 +15573,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H220" s="5" t="n">
+        <v>-0.006719</v>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>-0.006719</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -15750,17 +15598,19 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Issuance of founder shares during the</t>
+          <t>shares        capital       options      warrants        loss            deficit        Total</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Issuance of founder shares during the period (Note 6(b)(ii)) 2,065,000 154,875 - -</t>
+          <t>Share-based compensation (note 9) - - 163,673 - -</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
-      <c r="E221" s="5" t="n">
-        <v>0.154875</v>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -15772,10 +15622,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>0.163673</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -15801,17 +15649,19 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Issuance of shares under public</t>
+          <t>shares        capital       options      warrants        loss            deficit        Total</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 6(b)(ii)) - (128,642) - 39,874</t>
+          <t>Net loss and comprehensive for the period - - - - -</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" s="5" t="n">
-        <v>-0.088768</v>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -15823,15 +15673,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H222" s="5" t="n">
+        <v>-1.451529</v>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>-1.451529</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -15852,35 +15698,35 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Issuance of shares under public</t>
+          <t>shares        capital       options      warrants        loss            deficit        Total</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - -</t>
+          <t>Balance, December 31, 2022 56,809,749 6,271,465 647,311 - -</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" s="5" t="n">
-        <v>-0.154451</v>
-      </c>
-      <c r="F223" s="5" t="n">
-        <v>-0.154451</v>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H223" s="5" t="n">
+        <v>-0.7316589999999999</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>-7.650435</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -15901,30 +15747,32 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Issuance of shares under public</t>
+          <t>Shares deemed to be issued on reverse</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Balance – December 31, 2018 7,065,000 776,233 - 39,874</t>
+          <t>Shares deemed to be issued on reverse takeover (note 8) 1,413,000 353,250 - - -</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
-      <c r="E224" s="5" t="n">
-        <v>0.661656</v>
-      </c>
-      <c r="F224" s="5" t="n">
-        <v>-0.154451</v>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>0.35325</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -15950,17 +15798,19 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Issuance of shares under public</t>
+          <t>Shares issued related to concurrent</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Stock-based compensation - - 33,279 -</t>
+          <t>Shares issued related to concurrent financing (note 8) 18,705,600 4,676,400 - - -</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
-      <c r="E225" s="5" t="n">
-        <v>0.033279</v>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -15972,10 +15822,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H225" s="5" t="n">
+        <v>4.6764</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -16001,42 +15849,1807 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
+          <t>Share issue costs related to concurrent</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Share issue costs related to concurrent financing - - - - -</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>-0.451124</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>-0.451124</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Share issue costs related to concurrent</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Broker warrants granted (note 8) - - - 101,000 -</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" s="5" t="n">
+        <v>-0.101</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Share issue costs related to concurrent</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Exercise of warrants (note 8) 4,250,034 1,275,010 - - -</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>1.27501</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Share issue costs related to concurrent</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 9) - - 522,048 - -</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>0.522048</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period - - - - 15</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>-4.80729</v>
+      </c>
+      <c r="I230" s="5" t="n">
+        <v>-4.807305</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Balance, March 31, 2024 81,178,383 $ 12,576,125 $ 1,169,359 $ 101,000 $ 15 $</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>0.836635</v>
+      </c>
+      <c r="I231" s="5" t="n">
+        <v>-13.009864</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 9)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>0.221576</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>0.163673</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Management fees (note 15)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>0.244022</v>
+      </c>
+      <c r="H233" s="5" t="n">
+        <v>0.266376</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="n">
+        <v>0.068588</v>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>0.053302</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>0.484518</v>
+      </c>
+      <c r="H234" s="5" t="n">
+        <v>0.373182</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Write-off of deferred expenses (note 9)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>0.215349</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Office and travelling expenses</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>0.039149</v>
+      </c>
+      <c r="H236" s="5" t="n">
+        <v>0.114246</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Exploration expenses</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>0.449782</v>
+      </c>
+      <c r="H237" s="5" t="n">
+        <v>0.276958</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="n">
+        <v>-0.000958</v>
+      </c>
+      <c r="H238" s="5" t="n">
+        <v>-0.000307</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Depreciation of property, plant and</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Depreciation of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="n">
+        <v>0.023371</v>
+      </c>
+      <c r="H239" s="5" t="n">
+        <v>0.023888</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Depreciation of property, plant and</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Interest on long-term debt</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="n">
+        <v>0.004899</v>
+      </c>
+      <c r="H240" s="5" t="n">
+        <v>0.006119</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Amortization of deferred government grant</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Amortization of deferred government grant income</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="n">
+        <v>-0.004899</v>
+      </c>
+      <c r="H241" s="5" t="n">
+        <v>-0.006119</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Amortization of deferred government grant</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="n">
+        <v>0.005122</v>
+      </c>
+      <c r="H242" s="5" t="n">
+        <v>0.002809</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Amortization of deferred government grant</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Gain on sale of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="n">
+        <v>-0.002341</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Amortization of deferred government grant</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Sundry taxes</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>0.017696</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Amortization of deferred government grant</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G245" s="5" t="n">
+        <v>-1.466582</v>
+      </c>
+      <c r="H245" s="5" t="n">
+        <v>-1.451529</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Amortization of deferred government grant</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Basic and diluted net loss per share (note 11)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="H246" s="5" t="n">
+        <v>2.7e-08</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>For the year ended December 31, 2019 and for the period from April 27, 2018 to December</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F247" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>0.033279</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Listing fees</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" s="5" t="n">
+        <v>0.085689</v>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>0.005987</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Bank charges and interest</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" s="5" t="n">
+        <v>0.000174</v>
+      </c>
+      <c r="F250" s="5" t="n">
+        <v>2e-05</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" s="5" t="n">
+        <v>-0.154451</v>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>-0.092588</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted loss per share (Note 6(c))</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>For the year ended December 31, 2019 and for the period from April 27, 2018 to December</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>shares       Capital    Surplus         Warrants      Deficit         equity</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Balance - April 27, 2018 - - - -</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Issuance of founder shares during the</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Issuance of founder shares during the period (Note 6(b)(ii)) 2,065,000 154,875 - -</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" s="5" t="n">
+        <v>0.154875</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
           <t>Issuance of shares under public</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Share issuance costs (Note 6(b)(ii)) - (128,642) - 39,874</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" s="5" t="n">
+        <v>-0.088768</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Issuance of shares under public</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - - -</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" s="5" t="n">
+        <v>-0.154451</v>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>-0.154451</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Issuance of shares under public</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Balance – December 31, 2018 7,065,000 776,233 - 39,874</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" s="5" t="n">
+        <v>0.661656</v>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>-0.154451</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Issuance of shares under public</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Stock-based compensation - - 33,279 -</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" s="5" t="n">
+        <v>0.033279</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Issuance of shares under public</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
         <is>
           <t>Balance – December 31, 2019 7,065,000 776,233 33,279 39,874</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" s="5" t="n">
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" s="5" t="n">
         <v>0.602347</v>
       </c>
-      <c r="F226" s="5" t="n">
+      <c r="F260" s="5" t="n">
         <v>-0.247039</v>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="n">
+        <v>0.000174</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
         <is>
           <t>-</t>
         </is>
